--- a/modules/log/Kanat.xlsx
+++ b/modules/log/Kanat.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N306"/>
+  <dimension ref="A1:N309"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13863,10 +13863,142 @@
         <v>36</v>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>Kanat</v>
+      </c>
+      <c r="B307" t="str">
+        <v>9551</v>
+      </c>
+      <c r="C307" t="str">
+        <v>Жунисов К</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Абай (Комешбулак)</v>
+      </c>
+      <c r="E307" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F307" t="str">
+        <v>73434</v>
+      </c>
+      <c r="G307" t="str">
+        <v>180</v>
+      </c>
+      <c r="H307" t="str">
+        <v>201</v>
+      </c>
+      <c r="I307" t="str">
+        <v>21</v>
+      </c>
+      <c r="J307" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K307" t="str">
+        <v>12</v>
+      </c>
+      <c r="L307" t="str">
+        <v>23</v>
+      </c>
+      <c r="M307" t="str">
+        <v>15</v>
+      </c>
+      <c r="N307" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Kanat</v>
+      </c>
+      <c r="B308" t="str">
+        <v>9841</v>
+      </c>
+      <c r="C308" t="str">
+        <v>Султанбек Т</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Абай (Комешбулак)</v>
+      </c>
+      <c r="E308" t="str">
+        <v>48</v>
+      </c>
+      <c r="F308" t="str">
+        <v>82013</v>
+      </c>
+      <c r="G308" t="str">
+        <v>60</v>
+      </c>
+      <c r="H308" t="str">
+        <v>82</v>
+      </c>
+      <c r="I308" t="str">
+        <v>22</v>
+      </c>
+      <c r="J308" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K308" t="str">
+        <v>12</v>
+      </c>
+      <c r="L308" t="str">
+        <v>23</v>
+      </c>
+      <c r="M308" t="str">
+        <v>15</v>
+      </c>
+      <c r="N308" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Kanat</v>
+      </c>
+      <c r="B309" t="str">
+        <v>9733</v>
+      </c>
+      <c r="C309" t="str">
+        <v>Калыбеков Исабек</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Мусаев (Комешбулак)</v>
+      </c>
+      <c r="E309" t="str">
+        <v>30</v>
+      </c>
+      <c r="F309" t="str">
+        <v>68055</v>
+      </c>
+      <c r="G309" t="str">
+        <v>435</v>
+      </c>
+      <c r="H309" t="str">
+        <v>436</v>
+      </c>
+      <c r="I309" t="str">
+        <v>1</v>
+      </c>
+      <c r="J309" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K309" t="str">
+        <v>12</v>
+      </c>
+      <c r="L309" t="str">
+        <v>23</v>
+      </c>
+      <c r="M309" t="str">
+        <v>15</v>
+      </c>
+      <c r="N309" t="str">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N306"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N309"/>
   </ignoredErrors>
 </worksheet>
 </file>